--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>pGrl7dpe</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,85 +456,85 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>bqbA3PNE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.590162172286133</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.55630480654459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>6VWd5zF7</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.8061690805030673</v>
+        <v>-0.007391996240000759</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8047562165610213</v>
+        <v>0.01773587552581747</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>QDjsB5oT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.604946164766134</v>
+        <v>1.590162172286133</v>
       </c>
       <c r="C5" t="n">
-        <v>1.591776557596225</v>
+        <v>-1.55630480654459</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>ddsD5q9j</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.791385088023066</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.7692844655093862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.791385088023066</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0.7692844655093862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.8061690805030673</v>
+        <v>-0.007391996240000759</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8047562165610213</v>
+        <v>0.01773587552581747</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -542,279 +542,6 @@
       </c>
       <c r="C9" t="n">
         <v>0.01773587552581747</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>0AJjqex0</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>QmPfsURO</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>YJVCWCD6</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.791385088023066</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.7692844655093862</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.007391996240000759</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.01773587552581747</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.791385088023066</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.7692844655093862</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4vvdzeEs</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>-1.604946164766134</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.591776557596225</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.590162172286133</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-1.55630480654459</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>-0.8061690805030673</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.8047562165610213</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.057644116110755</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.031624579187787</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>pGrl7dpe</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>6VWd5zF7</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>-0.007391996240000759</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.01773587552581747</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>bqbA3PNE</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>QDjsB5oT</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1.590162172286133</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-1.55630480654459</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>ddsD5q9j</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>f5SjRHyR</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0.791385088023066</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.7692844655093862</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>bwZsTw7E</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>-0.007391996240000759</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.01773587552581747</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>rkN7RQV9</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>-0.007391996240000759</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.01773587552581747</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>445r4WXo</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>-0.5399100524153786</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.54241610288262</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,365 +456,105 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.590162172286133</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.55630480654459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.8061690805030673</v>
+        <v>-0.007391996240000759</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8047562165610213</v>
+        <v>0.01773587552581747</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.604946164766134</v>
+        <v>0.791385088023066</v>
       </c>
       <c r="C5" t="n">
-        <v>1.591776557596225</v>
+        <v>-0.7692844655093862</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>4vvdzeEs</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.791385088023066</v>
+        <v>-1.604946164766134</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.7692844655093862</v>
+        <v>1.591776557596225</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>YemQuHjK</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1.590162172286133</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-1.55630480654459</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>KSw0hfzQ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.8061690805030673</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8047562165610213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>hMoEUjrJ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.007391996240000759</v>
+        <v>-0.8061690805030673</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01773587552581747</v>
+        <v>0.8047562165610213</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>06X4YYrf</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.2588670318476882</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>QmPfsURO</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>YJVCWCD6</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.791385088023066</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.7692844655093862</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.007391996240000759</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.01773587552581747</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.791385088023066</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.7692844655093862</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4vvdzeEs</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>-1.604946164766134</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.591776557596225</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.590162172286133</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-1.55630480654459</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>-0.8061690805030673</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.8047562165610213</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.057644116110755</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.031624579187787</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>pGrl7dpe</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>6VWd5zF7</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>-0.007391996240000759</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.01773587552581747</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>bqbA3PNE</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>QDjsB5oT</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1.590162172286133</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-1.55630480654459</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>ddsD5q9j</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>f5SjRHyR</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0.791385088023066</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.7692844655093862</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>bwZsTw7E</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>-0.007391996240000759</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.01773587552581747</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>rkN7RQV9</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>-0.007391996240000759</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.01773587552581747</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>445r4WXo</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>-0.5399100524153786</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.54241610288262</v>
+        <v>-0.2446042381525837</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,20 +443,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.791385088023066</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0.7692844655093862</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -469,92 +469,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.007391996240000759</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01773587552581747</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.791385088023066</v>
+        <v>-0.007391996240000759</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.7692844655093862</v>
+        <v>0.01773587552581747</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.604946164766134</v>
+        <v>0.791385088023066</v>
       </c>
       <c r="C6" t="n">
-        <v>1.591776557596225</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.590162172286133</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-1.55630480654459</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>-0.8061690805030673</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.8047562165610213</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.2588670318476882</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.2446042381525837</v>
+        <v>-0.7692844655093862</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,38 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_red_cards</t>
+          <t>dif_mean_last_30_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_red_cards_against</t>
+          <t>dif_mean_last_30_matches_KGP_against</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.791385088023066</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.7692844655093862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -469,7 +469,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -482,27 +482,131 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.007391996240000759</v>
+        <v>0.09272344995743113</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01773587552581747</v>
+        <v>-1.583126244040831</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.791385088023066</v>
+        <v>-0.647637281785559</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.7692844655093862</v>
+        <v>-0.2946749021016778</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.8947809093456706</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.326465707625869</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3395103605384279</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-2.121085646899331</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.2778136328931787</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.09987253095655256</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.005322006960156</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.827609550410598</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EB22wLQj</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.9561209200118049</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.6353054091899147</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.709690726409923</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.7292591595156573</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-1.573088196464297</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6.006622913511595</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-1.819875107045294</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9553631176160025</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,7 +456,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -469,7 +469,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -482,131 +482,131 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09272344995743113</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.583126244040831</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.647637281785559</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2946749021016778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8947809093456706</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.326465707625869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3395103605384279</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.121085646899331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2778136328931787</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.09987253095655256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.005322006960156</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.827609550410598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.9561209200118049</v>
+        <v>0.09272344995743113</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.6353054091899147</v>
+        <v>-1.583126244040831</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.709690726409923</v>
+        <v>-0.647637281785559</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.7292591595156573</v>
+        <v>-0.2946749021016778</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.573088196464297</v>
+        <v>0.8947809093456706</v>
       </c>
       <c r="C13" t="n">
-        <v>6.006622913511595</v>
+        <v>-1.326465707625869</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.819875107045294</v>
+        <v>0.3395103605384279</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9553631176160025</v>
+        <v>-2.121085646899331</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,188 +425,409 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_30_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_30_matches_dangerous_attacks</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_KGP_against</t>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_total_passes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>E595Qvn9</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>jiAoNQdE</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>842EOIGL</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>naHJ2yf2</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>02sgHz9e</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>4zlpJdvq</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>8Sp1FEw8</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09272344995743113</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.583126244040831</v>
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.647637281785559</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2946749021016778</v>
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8947809093456706</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.326465707625869</v>
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3395103605384279</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>-2.121085646899331</v>
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>65kl1OIc</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0SQqjbAd</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8Uo5ctIM</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h2NyhKup</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E595Qvn9</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jiAoNQdE</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -491,7 +491,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>842EOIGL</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -510,7 +510,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>naHJ2yf2</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -529,7 +529,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>02sgHz9e</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -542,291 +542,6 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>4zlpJdvq</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8Sp1FEw8</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>dhkQFrkl</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>x88gL4RQ</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>vymauDyP</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>QqTA4cPk</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>2Xrca2mA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>f1xuAJ1S</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>65kl1OIc</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0SQqjbAd</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>8Uo5ctIM</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>h2NyhKup</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ll7vCuXF</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YNHbsZ6C</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Gz9WD123</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,35 +425,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_PPS_against</t>
+          <t>dif_mean_last_30_matches_attacks</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_30_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_30_matches_dangerous_attacks</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_total_passes_against</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_total_passes</t>
+          <t>dif_mean_last_30_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_KGP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_KGP_against</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -466,13 +476,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -485,13 +501,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -504,13 +526,19 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -523,13 +551,19 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -542,6 +576,387 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dhkQFrkl</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>x88gL4RQ</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vymauDyP</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zeCiJHet</t>
+          <t>E595Qvn9</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5mYDMJ0</t>
+          <t>jiAoNQdE</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -513,7 +513,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>842EOIGL</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>naHJ2yf2</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>02sgHz9e</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -588,7 +588,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zHmSVfun</t>
+          <t>4zlpJdvq</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YFePBifU</t>
+          <t>8Sp1FEw8</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -638,7 +638,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dA00HeQh</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4z48FZf5</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -688,7 +688,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>02cHDDPH</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -707,256 +707,6 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>E595Qvn9</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>jiAoNQdE</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>842EOIGL</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>naHJ2yf2</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>02sgHz9e</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4zlpJdvq</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>8Sp1FEw8</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dhkQFrkl</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>x88gL4RQ</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vymauDyP</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E595Qvn9</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jiAoNQdE</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -513,7 +513,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>842EOIGL</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>naHJ2yf2</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>02sgHz9e</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -588,7 +588,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4zlpJdvq</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8Sp1FEw8</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -638,7 +638,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dhkQFrkl</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>x88gL4RQ</t>
+          <t>nucZxUhT</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -688,7 +688,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vymauDyP</t>
+          <t>rPc4X7Gj</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -707,6 +707,256 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zeCiJHet</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -513,7 +513,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -588,7 +588,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>dA00HeQh</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>4z48FZf5</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -638,7 +638,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bXuieB8c</t>
+          <t>02cHDDPH</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -657,306 +657,6 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>nucZxUhT</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rPc4X7Gj</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>rsizUY9b</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>UaS8aGMt</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>QXtsC0lD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>zHmSVfun</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>YFePBifU</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dA00HeQh</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>4z48FZf5</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>02cHDDPH</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,238 +425,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_attacks</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_attacks_against</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>dif_mean_last_30_matches_dangerous_attacks</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_dangerous_attacks_against</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_KGP</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_KGP_against</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zeCiJHet</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5mYDMJ0</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dA00HeQh</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4z48FZf5</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>02cHDDPH</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nucZxUhT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rPc4X7Gj</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,113 +425,247 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_dangerous_attacks</t>
+          <t>dif_mean_last_60_matches_attacks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>IsCnpo0d</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>buKPeYL5</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>vVwOqx6D</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>C2KEmK6l</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
+          <t>SCX7iT7M</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-0.9633490247189468</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-2.054642297196725</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.043221880326451</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bXuieB8c</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nucZxUhT</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>4duqSCvB</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>UwPNKUWp</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>bXuieB8c</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nucZxUhT</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
           <t>rPc4X7Gj</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
         <v>0</v>
       </c>
     </row>
